--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/37.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/37.xlsx
@@ -426,13 +426,13 @@
         <v>-7.549441727415897</v>
       </c>
       <c r="E2">
-        <v>-7.599370163199459</v>
+        <v>-5.827111104031595</v>
       </c>
       <c r="F2">
-        <v>-3.093345203397409</v>
+        <v>-2.730898844874305</v>
       </c>
       <c r="G2">
-        <v>-5.737441413868443</v>
+        <v>-4.403132655356269</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.800292344095184</v>
       </c>
       <c r="E3">
-        <v>-8.412625224814956</v>
+        <v>-7.156834097747889</v>
       </c>
       <c r="F3">
-        <v>-3.023104617844428</v>
+        <v>-2.795866043541065</v>
       </c>
       <c r="G3">
-        <v>-5.14962756900653</v>
+        <v>-3.641141078036681</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.054074618298854</v>
       </c>
       <c r="E4">
-        <v>-8.561919955899832</v>
+        <v>-7.50404125686399</v>
       </c>
       <c r="F4">
-        <v>-3.252763681698771</v>
+        <v>-3.143467229838599</v>
       </c>
       <c r="G4">
-        <v>-5.118323050387181</v>
+        <v>-3.55679168824159</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.429153431330814</v>
       </c>
       <c r="E5">
-        <v>-9.606000394634302</v>
+        <v>-7.63414431510436</v>
       </c>
       <c r="F5">
-        <v>-3.107272544540677</v>
+        <v>-2.84442742579538</v>
       </c>
       <c r="G5">
-        <v>-4.706564017303709</v>
+        <v>-3.533813191653509</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.916123369920983</v>
       </c>
       <c r="E6">
-        <v>-9.616864203778702</v>
+        <v>-9.284655350576006</v>
       </c>
       <c r="F6">
-        <v>-3.582396750662181</v>
+        <v>-3.221343706110586</v>
       </c>
       <c r="G6">
-        <v>-4.311142526456541</v>
+        <v>-3.282589132860376</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.542440503026146</v>
       </c>
       <c r="E7">
-        <v>-9.878401691617697</v>
+        <v>-10.02602994426775</v>
       </c>
       <c r="F7">
-        <v>-3.444735342195348</v>
+        <v>-3.018335706706511</v>
       </c>
       <c r="G7">
-        <v>-4.153808849702678</v>
+        <v>-3.349475394935811</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.304948167151666</v>
       </c>
       <c r="E8">
-        <v>-11.43241547445989</v>
+        <v>-10.33156155709126</v>
       </c>
       <c r="F8">
-        <v>-3.43700418922502</v>
+        <v>-2.918380754047709</v>
       </c>
       <c r="G8">
-        <v>-3.233824797066911</v>
+        <v>-2.836986392728935</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.199940267793695</v>
       </c>
       <c r="E9">
-        <v>-12.54021154248229</v>
+        <v>-11.3734954991461</v>
       </c>
       <c r="F9">
-        <v>-3.29237206906363</v>
+        <v>-2.876907711659149</v>
       </c>
       <c r="G9">
-        <v>-3.458574423182493</v>
+        <v>-2.258167300097221</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.213126991364581</v>
       </c>
       <c r="E10">
-        <v>-13.22826788320772</v>
+        <v>-12.59930359980838</v>
       </c>
       <c r="F10">
-        <v>-3.429015413992422</v>
+        <v>-2.666129626016815</v>
       </c>
       <c r="G10">
-        <v>-3.206453206548217</v>
+        <v>-1.903909132485351</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.315705019059442</v>
       </c>
       <c r="E11">
-        <v>-13.30203672479267</v>
+        <v>-13.03692627096163</v>
       </c>
       <c r="F11">
-        <v>-3.451696941848475</v>
+        <v>-2.858449200822567</v>
       </c>
       <c r="G11">
-        <v>-2.706183427926791</v>
+        <v>-2.157344635698717</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.486226569623044</v>
       </c>
       <c r="E12">
-        <v>-14.99245267321991</v>
+        <v>-14.14377135944241</v>
       </c>
       <c r="F12">
-        <v>-3.404634076225824</v>
+        <v>-3.149559872086189</v>
       </c>
       <c r="G12">
-        <v>-2.592002712277328</v>
+        <v>-1.201765597424707</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.685569580523819</v>
       </c>
       <c r="E13">
-        <v>-15.28873714211976</v>
+        <v>-14.45520810237192</v>
       </c>
       <c r="F13">
-        <v>-3.081885568747081</v>
+        <v>-2.737203549177012</v>
       </c>
       <c r="G13">
-        <v>-1.649636061250549</v>
+        <v>-0.8352385480442973</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.889996508446897</v>
       </c>
       <c r="E14">
-        <v>-17.32870147072506</v>
+        <v>-15.86935543701321</v>
       </c>
       <c r="F14">
-        <v>-2.844361156403156</v>
+        <v>-2.499395006813927</v>
       </c>
       <c r="G14">
-        <v>-1.931883242292192</v>
+        <v>-0.8557506882056216</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.066388989665452</v>
       </c>
       <c r="E15">
-        <v>-17.07908745494826</v>
+        <v>-16.6852641843972</v>
       </c>
       <c r="F15">
-        <v>-2.757921017921028</v>
+        <v>-2.671601821079708</v>
       </c>
       <c r="G15">
-        <v>-1.682701790096789</v>
+        <v>-0.01055516984753046</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.197765254452431</v>
       </c>
       <c r="E16">
-        <v>-18.05313957162812</v>
+        <v>-16.57318898118137</v>
       </c>
       <c r="F16">
-        <v>-2.661645673265461</v>
+        <v>-2.02874398466754</v>
       </c>
       <c r="G16">
-        <v>-2.122527628262202</v>
+        <v>0.4974083166071619</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.274053363001402</v>
       </c>
       <c r="E17">
-        <v>-19.8568171834612</v>
+        <v>-18.61832935557744</v>
       </c>
       <c r="F17">
-        <v>-2.237473517722751</v>
+        <v>-2.227469324599142</v>
       </c>
       <c r="G17">
-        <v>-1.428537966864783</v>
+        <v>0.1924971408036678</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.295099628488332</v>
       </c>
       <c r="E18">
-        <v>-19.37115646003458</v>
+        <v>-19.03494896428311</v>
       </c>
       <c r="F18">
-        <v>-1.853027377716098</v>
+        <v>-1.727017785137043</v>
       </c>
       <c r="G18">
-        <v>-2.365438907206225</v>
+        <v>0.5130407126436005</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.274365603125879</v>
       </c>
       <c r="E19">
-        <v>-20.41548596483948</v>
+        <v>-18.83301072285907</v>
       </c>
       <c r="F19">
-        <v>-1.564864037671637</v>
+        <v>-1.180744274421687</v>
       </c>
       <c r="G19">
-        <v>-2.62424411528429</v>
+        <v>0.5765369760868219</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.223273442480878</v>
       </c>
       <c r="E20">
-        <v>-21.00285621447837</v>
+        <v>-19.38275388196823</v>
       </c>
       <c r="F20">
-        <v>-1.661208965189039</v>
+        <v>-1.296982445117319</v>
       </c>
       <c r="G20">
-        <v>-2.162869936203761</v>
+        <v>0.5258591449716585</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.167307785318533</v>
       </c>
       <c r="E21">
-        <v>-22.25542759652598</v>
+        <v>-21.32133473448981</v>
       </c>
       <c r="F21">
-        <v>-1.17233303181366</v>
+        <v>-0.7037355324588137</v>
       </c>
       <c r="G21">
-        <v>-1.764816561652872</v>
+        <v>-0.01742786238705744</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.117569109274298</v>
       </c>
       <c r="E22">
-        <v>-22.10981904328335</v>
+        <v>-21.17362496930762</v>
       </c>
       <c r="F22">
-        <v>-0.7225618384222381</v>
+        <v>-0.4182536176972145</v>
       </c>
       <c r="G22">
-        <v>-2.498933345531797</v>
+        <v>0.03916260306124423</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.093800759216411</v>
       </c>
       <c r="E23">
-        <v>-23.08251714623491</v>
+        <v>-21.56113554709198</v>
       </c>
       <c r="F23">
-        <v>-0.4074533634995146</v>
+        <v>-0.4093917432220654</v>
       </c>
       <c r="G23">
-        <v>-3.31427767476228</v>
+        <v>-0.283413643739801</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.098667059687803</v>
       </c>
       <c r="E24">
-        <v>-23.94753719423209</v>
+        <v>-22.34625067122382</v>
       </c>
       <c r="F24">
-        <v>-0.2673143081309082</v>
+        <v>-0.09719000951576534</v>
       </c>
       <c r="G24">
-        <v>-3.454485899441493</v>
+        <v>-0.8498148800537083</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.135021975623435</v>
       </c>
       <c r="E25">
-        <v>-22.77110304567544</v>
+        <v>-22.58242417614585</v>
       </c>
       <c r="F25">
-        <v>-0.1339744924044802</v>
+        <v>0.008638896396288292</v>
       </c>
       <c r="G25">
-        <v>-3.883923245704673</v>
+        <v>-0.7049387861641226</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.195862161418431</v>
       </c>
       <c r="E26">
-        <v>-23.11742715236004</v>
+        <v>-22.65330837978791</v>
       </c>
       <c r="F26">
-        <v>-0.1736905675317025</v>
+        <v>-0.07872901357697557</v>
       </c>
       <c r="G26">
-        <v>-3.817255479634829</v>
+        <v>-0.6369070753320998</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.269553082891701</v>
       </c>
       <c r="E27">
-        <v>-23.96429707653447</v>
+        <v>-21.30415370410471</v>
       </c>
       <c r="F27">
-        <v>-0.1045351432763886</v>
+        <v>0.2548976146353309</v>
       </c>
       <c r="G27">
-        <v>-4.170434409400897</v>
+        <v>-1.857816406942078</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.344966581114026</v>
       </c>
       <c r="E28">
-        <v>-23.52659289284909</v>
+        <v>-22.08131682787907</v>
       </c>
       <c r="F28">
-        <v>0.06318109129881613</v>
+        <v>0.3826749432519603</v>
       </c>
       <c r="G28">
-        <v>-4.323709357323614</v>
+        <v>-2.104898973265583</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.402280671425149</v>
       </c>
       <c r="E29">
-        <v>-23.51590116571698</v>
+        <v>-22.47243207097354</v>
       </c>
       <c r="F29">
-        <v>-0.06765871160596297</v>
+        <v>0.322680434104206</v>
       </c>
       <c r="G29">
-        <v>-4.901353206288887</v>
+        <v>-2.329161949186892</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.431855546612666</v>
       </c>
       <c r="E30">
-        <v>-22.7564398468386</v>
+        <v>-21.54652668994324</v>
       </c>
       <c r="F30">
-        <v>0.02230944364468853</v>
+        <v>0.3817289476779632</v>
       </c>
       <c r="G30">
-        <v>-4.653039117024773</v>
+        <v>-2.362816955139122</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.414034107270229</v>
       </c>
       <c r="E31">
-        <v>-22.61367970374679</v>
+        <v>-20.0095535547919</v>
       </c>
       <c r="F31">
-        <v>-0.09219329734207873</v>
+        <v>0.8264181070532106</v>
       </c>
       <c r="G31">
-        <v>-5.068883363303705</v>
+        <v>-2.687177585985835</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.343875805344843</v>
       </c>
       <c r="E32">
-        <v>-21.97625170242711</v>
+        <v>-20.77949376252403</v>
       </c>
       <c r="F32">
-        <v>0.04344192445750672</v>
+        <v>0.07791857576202214</v>
       </c>
       <c r="G32">
-        <v>-5.025852892384258</v>
+        <v>-2.399223024434488</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.211024311506979</v>
       </c>
       <c r="E33">
-        <v>-21.21906367750058</v>
+        <v>-20.6774536577092</v>
       </c>
       <c r="F33">
-        <v>-0.5641489981478747</v>
+        <v>0.124040416015093</v>
       </c>
       <c r="G33">
-        <v>-5.085790319372763</v>
+        <v>-2.787278551456778</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.0175519673517</v>
       </c>
       <c r="E34">
-        <v>-20.81916772330523</v>
+        <v>-20.55214172496894</v>
       </c>
       <c r="F34">
-        <v>0.001413047541668204</v>
+        <v>0.2614806503853786</v>
       </c>
       <c r="G34">
-        <v>-4.472624316771111</v>
+        <v>-2.879510350180873</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.7687654094826</v>
       </c>
       <c r="E35">
-        <v>-20.24557762007169</v>
+        <v>-19.48555929889036</v>
       </c>
       <c r="F35">
-        <v>-0.130686702182769</v>
+        <v>0.0480136841535572</v>
       </c>
       <c r="G35">
-        <v>-4.938980866888243</v>
+        <v>-2.803198964955133</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.476314489783968</v>
       </c>
       <c r="E36">
-        <v>-20.12472623422898</v>
+        <v>-19.17260551716828</v>
       </c>
       <c r="F36">
-        <v>-0.3842275982598221</v>
+        <v>-0.1014610718445996</v>
       </c>
       <c r="G36">
-        <v>-4.793538669711442</v>
+        <v>-2.894083371644745</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.159476671150038</v>
       </c>
       <c r="E37">
-        <v>-19.47338676075774</v>
+        <v>-18.05099307494848</v>
       </c>
       <c r="F37">
-        <v>-0.2819540452405839</v>
+        <v>0.1336478211527617</v>
       </c>
       <c r="G37">
-        <v>-3.931730833837288</v>
+        <v>-2.573937065269525</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.834311651589498</v>
       </c>
       <c r="E38">
-        <v>-19.69285019659147</v>
+        <v>-18.37521370000165</v>
       </c>
       <c r="F38">
-        <v>-0.518645948344695</v>
+        <v>-0.1049037667706343</v>
       </c>
       <c r="G38">
-        <v>-4.175982883724716</v>
+        <v>-2.058481814259462</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.526531487550171</v>
       </c>
       <c r="E39">
-        <v>-19.23494449035787</v>
+        <v>-17.58243639784884</v>
       </c>
       <c r="F39">
-        <v>-0.9041408014832926</v>
+        <v>-0.2381599173893796</v>
       </c>
       <c r="G39">
-        <v>-3.620238293501723</v>
+        <v>-2.058276560436027</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.249892330029113</v>
       </c>
       <c r="E40">
-        <v>-17.98512189203291</v>
+        <v>-17.51568216250177</v>
       </c>
       <c r="F40">
-        <v>-0.740551493308835</v>
+        <v>-0.3630744082619339</v>
       </c>
       <c r="G40">
-        <v>-3.727582732612591</v>
+        <v>-2.060620426677831</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.026130560333815</v>
       </c>
       <c r="E41">
-        <v>-17.64250207708658</v>
+        <v>-16.83412871045135</v>
       </c>
       <c r="F41">
-        <v>-0.7631824907533175</v>
+        <v>-0.471529238840862</v>
       </c>
       <c r="G41">
-        <v>-3.5708284013281</v>
+        <v>-1.39502862491628</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.861135432656322</v>
       </c>
       <c r="E42">
-        <v>-17.57002385059381</v>
+        <v>-16.74755787284672</v>
       </c>
       <c r="F42">
-        <v>-1.093228915050724</v>
+        <v>-0.6568201162338609</v>
       </c>
       <c r="G42">
-        <v>-2.847576827909063</v>
+        <v>-1.607774212906464</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.761448200693256</v>
       </c>
       <c r="E43">
-        <v>-17.18352765098717</v>
+        <v>-16.58163911367968</v>
       </c>
       <c r="F43">
-        <v>-0.9784221632271298</v>
+        <v>-0.2979324240731835</v>
       </c>
       <c r="G43">
-        <v>-3.327595999466768</v>
+        <v>-1.140361598762305</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.722666358184886</v>
       </c>
       <c r="E44">
-        <v>-17.09346083144861</v>
+        <v>-15.06768421190934</v>
       </c>
       <c r="F44">
-        <v>-1.18579317374175</v>
+        <v>-0.4153236821935127</v>
       </c>
       <c r="G44">
-        <v>-3.109573401886985</v>
+        <v>-1.12198807101935</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.736479384773107</v>
       </c>
       <c r="E45">
-        <v>-16.66398488503516</v>
+        <v>-14.42984411945496</v>
       </c>
       <c r="F45">
-        <v>-1.293972986342948</v>
+        <v>-0.7343652455447283</v>
       </c>
       <c r="G45">
-        <v>-2.570745699369667</v>
+        <v>-0.948863092043163</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.793472503908734</v>
       </c>
       <c r="E46">
-        <v>-15.70654773948945</v>
+        <v>-13.9779295843335</v>
       </c>
       <c r="F46">
-        <v>-1.452506768258121</v>
+        <v>-0.9351474217374809</v>
       </c>
       <c r="G46">
-        <v>-2.899833789246459</v>
+        <v>-0.9979022031163871</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.876927522486381</v>
       </c>
       <c r="E47">
-        <v>-14.38071470494574</v>
+        <v>-13.51036011456753</v>
       </c>
       <c r="F47">
-        <v>-1.836720137024587</v>
+        <v>-1.194978939871393</v>
       </c>
       <c r="G47">
-        <v>-3.126576363776682</v>
+        <v>-1.514416828699017</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.977711961086142</v>
       </c>
       <c r="E48">
-        <v>-13.55871968849544</v>
+        <v>-13.07958902458789</v>
       </c>
       <c r="F48">
-        <v>-1.952958307720219</v>
+        <v>-1.24668894662375</v>
       </c>
       <c r="G48">
-        <v>-2.515307303769032</v>
+        <v>-1.308527380520663</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.078055195737847</v>
       </c>
       <c r="E49">
-        <v>-13.83769632973797</v>
+        <v>-12.33046168339501</v>
       </c>
       <c r="F49">
-        <v>-1.981795433746476</v>
+        <v>-1.010904105825704</v>
       </c>
       <c r="G49">
-        <v>-3.175420152663089</v>
+        <v>-0.8240720779403357</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.174803510022416</v>
       </c>
       <c r="E50">
-        <v>-13.61877178231116</v>
+        <v>-12.46829484676647</v>
       </c>
       <c r="F50">
-        <v>-1.680550515677005</v>
+        <v>-1.119183322515239</v>
       </c>
       <c r="G50">
-        <v>-2.662682859540768</v>
+        <v>-0.8607198170600676</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.260639779578265</v>
       </c>
       <c r="E51">
-        <v>-13.54017558743403</v>
+        <v>-11.73302463603707</v>
       </c>
       <c r="F51">
-        <v>-1.97144912488551</v>
+        <v>-1.141033997866284</v>
       </c>
       <c r="G51">
-        <v>-3.201265581688179</v>
+        <v>-1.401580194538498</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.339408852454393</v>
       </c>
       <c r="E52">
-        <v>-12.72191203356605</v>
+        <v>-11.07537246979913</v>
       </c>
       <c r="F52">
-        <v>-1.818042108826264</v>
+        <v>-1.518160683501801</v>
       </c>
       <c r="G52">
-        <v>-2.719743422455646</v>
+        <v>-0.8915873436682322</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.413649352025717</v>
       </c>
       <c r="E53">
-        <v>-12.47594796783944</v>
+        <v>-11.2641011525428</v>
       </c>
       <c r="F53">
-        <v>-1.887576096984657</v>
+        <v>-1.427170322876095</v>
       </c>
       <c r="G53">
-        <v>-3.363972273852279</v>
+        <v>-1.229537763953653</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.488705865227168</v>
       </c>
       <c r="E54">
-        <v>-12.31453956878404</v>
+        <v>-10.09477670817819</v>
       </c>
       <c r="F54">
-        <v>-2.062984551262258</v>
+        <v>-1.162789410966007</v>
       </c>
       <c r="G54">
-        <v>-3.35565618345763</v>
+        <v>-1.484280932655031</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.570711280765794</v>
       </c>
       <c r="E55">
-        <v>-11.70331331807274</v>
+        <v>-9.917296754869577</v>
       </c>
       <c r="F55">
-        <v>-2.348895560338507</v>
+        <v>-1.169991237165946</v>
       </c>
       <c r="G55">
-        <v>-3.803503473464697</v>
+        <v>-1.42078466921181</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.660110501988771</v>
       </c>
       <c r="E56">
-        <v>-11.49302909905256</v>
+        <v>-9.10314958387457</v>
       </c>
       <c r="F56">
-        <v>-1.945013435959969</v>
+        <v>-1.385283925153538</v>
       </c>
       <c r="G56">
-        <v>-4.038135078015003</v>
+        <v>-1.996445501399059</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.761944942883651</v>
       </c>
       <c r="E57">
-        <v>-11.11503737363232</v>
+        <v>-9.724614714317211</v>
       </c>
       <c r="F57">
-        <v>-1.795139406873663</v>
+        <v>-1.746792571776673</v>
       </c>
       <c r="G57">
-        <v>-4.196935326442763</v>
+        <v>-2.407304066095849</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.869813272097711</v>
       </c>
       <c r="E58">
-        <v>-10.63778149796394</v>
+        <v>-8.711173930718639</v>
       </c>
       <c r="F58">
-        <v>-1.915238598033744</v>
+        <v>-1.45107452101868</v>
       </c>
       <c r="G58">
-        <v>-4.799749253143115</v>
+        <v>-2.442697108456197</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.984814319020451</v>
       </c>
       <c r="E59">
-        <v>-10.32986337933839</v>
+        <v>-8.190227337824256</v>
       </c>
       <c r="F59">
-        <v>-2.363455774177514</v>
+        <v>-1.755844970754466</v>
       </c>
       <c r="G59">
-        <v>-4.150706868532381</v>
+        <v>-2.049751905672403</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.09674914032075</v>
       </c>
       <c r="E60">
-        <v>-10.04334682887308</v>
+        <v>-7.906405229393517</v>
       </c>
       <c r="F60">
-        <v>-2.127393430299531</v>
+        <v>-1.680331826682666</v>
       </c>
       <c r="G60">
-        <v>-4.915985817572465</v>
+        <v>-2.761889977716107</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.202277399710074</v>
       </c>
       <c r="E61">
-        <v>-10.90001637080011</v>
+        <v>-8.307111780436236</v>
       </c>
       <c r="F61">
-        <v>-2.475977888704188</v>
+        <v>-1.654280500232024</v>
       </c>
       <c r="G61">
-        <v>-4.696096072308534</v>
+        <v>-2.738613532029492</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.293633635603989</v>
       </c>
       <c r="E62">
-        <v>-9.661293062267957</v>
+        <v>-8.372815409813525</v>
       </c>
       <c r="F62">
-        <v>-2.468683285355135</v>
+        <v>-1.57284535759761</v>
       </c>
       <c r="G62">
-        <v>-5.080821190518317</v>
+        <v>-3.337991112460079</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.366842446864512</v>
       </c>
       <c r="E63">
-        <v>-8.488545091553549</v>
+        <v>-7.669901145868924</v>
       </c>
       <c r="F63">
-        <v>-2.393823723164144</v>
+        <v>-1.661250383559179</v>
       </c>
       <c r="G63">
-        <v>-5.083909929506457</v>
+        <v>-3.251403793880441</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.421398825085349</v>
       </c>
       <c r="E64">
-        <v>-9.385640320947054</v>
+        <v>-7.305544655685775</v>
       </c>
       <c r="F64">
-        <v>-2.360327858864543</v>
+        <v>-1.737738516064074</v>
       </c>
       <c r="G64">
-        <v>-5.773705129705619</v>
+        <v>-3.218374481035132</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.455695003839421</v>
       </c>
       <c r="E65">
-        <v>-8.720158423149858</v>
+        <v>-7.633528442639316</v>
       </c>
       <c r="F65">
-        <v>-2.622895474529903</v>
+        <v>-2.077541451631654</v>
       </c>
       <c r="G65">
-        <v>-5.691563873785222</v>
+        <v>-3.101866451871562</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.478781629738042</v>
       </c>
       <c r="E66">
-        <v>-8.83839687949013</v>
+        <v>-7.396476413759796</v>
       </c>
       <c r="F66">
-        <v>-2.643009063437277</v>
+        <v>-1.899175725726059</v>
       </c>
       <c r="G66">
-        <v>-5.676361848668889</v>
+        <v>-2.808442869089339</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.491744276550817</v>
       </c>
       <c r="E67">
-        <v>-9.140396282587659</v>
+        <v>-7.127924319682921</v>
       </c>
       <c r="F67">
-        <v>-2.544001763087278</v>
+        <v>-2.020650835142189</v>
       </c>
       <c r="G67">
-        <v>-5.545251003131593</v>
+        <v>-3.439820182702522</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.50790981804625</v>
       </c>
       <c r="E68">
-        <v>-8.436354428615148</v>
+        <v>-7.607639156737465</v>
       </c>
       <c r="F68">
-        <v>-2.74555017912762</v>
+        <v>-2.047055874473827</v>
       </c>
       <c r="G68">
-        <v>-5.648722103961514</v>
+        <v>-3.156689086001892</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.528398003257857</v>
       </c>
       <c r="E69">
-        <v>-8.236010210041805</v>
+        <v>-7.294644618749313</v>
       </c>
       <c r="F69">
-        <v>-2.706141428306836</v>
+        <v>-2.069060626161793</v>
       </c>
       <c r="G69">
-        <v>-5.69688723101237</v>
+        <v>-3.318346335230044</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.562067413748764</v>
       </c>
       <c r="E70">
-        <v>-8.445760069129079</v>
+        <v>-7.456465108939406</v>
       </c>
       <c r="F70">
-        <v>-3.131375550859934</v>
+        <v>-2.216971424503464</v>
       </c>
       <c r="G70">
-        <v>-5.567845476437119</v>
+        <v>-3.527427149308255</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.609436499165763</v>
       </c>
       <c r="E71">
-        <v>-8.529292300674566</v>
+        <v>-7.428451968727956</v>
       </c>
       <c r="F71">
-        <v>-2.69684548931262</v>
+        <v>-2.265703450442756</v>
       </c>
       <c r="G71">
-        <v>-5.70711019563764</v>
+        <v>-3.397117455791463</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.671603105090198</v>
       </c>
       <c r="E72">
-        <v>-8.88465976995249</v>
+        <v>-7.35032220667362</v>
       </c>
       <c r="F72">
-        <v>-2.926957670136295</v>
+        <v>-1.9958577987764</v>
       </c>
       <c r="G72">
-        <v>-5.452360405845183</v>
+        <v>-3.366547878281832</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.747046205345648</v>
       </c>
       <c r="E73">
-        <v>-8.788529323717665</v>
+        <v>-7.878546057298329</v>
       </c>
       <c r="F73">
-        <v>-2.747341937819875</v>
+        <v>-2.489268215314703</v>
       </c>
       <c r="G73">
-        <v>-5.874550967922898</v>
+        <v>-3.765673869587445</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.826913098096564</v>
       </c>
       <c r="E74">
-        <v>-9.287888681017481</v>
+        <v>-8.59881796211433</v>
       </c>
       <c r="F74">
-        <v>-2.781981777502742</v>
+        <v>-2.295678753280459</v>
       </c>
       <c r="G74">
-        <v>-5.717766841728555</v>
+        <v>-3.319640758535899</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.906529668207318</v>
       </c>
       <c r="E75">
-        <v>-10.65230884258055</v>
+        <v>-7.764772676329619</v>
       </c>
       <c r="F75">
-        <v>-2.697402152207301</v>
+        <v>-2.561536644269738</v>
       </c>
       <c r="G75">
-        <v>-6.046454355595094</v>
+        <v>-3.3592448148222</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.969892630876385</v>
       </c>
       <c r="E76">
-        <v>-10.39847881750261</v>
+        <v>-8.713451753144497</v>
       </c>
       <c r="F76">
-        <v>-2.853812828469099</v>
+        <v>-2.610541203084551</v>
       </c>
       <c r="G76">
-        <v>-5.140824828417608</v>
+        <v>-3.371222368583283</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.01242539244878</v>
       </c>
       <c r="E77">
-        <v>-10.71688035345592</v>
+        <v>-8.528237166230779</v>
       </c>
       <c r="F77">
-        <v>-2.879253648143877</v>
+        <v>-2.436773744631896</v>
       </c>
       <c r="G77">
-        <v>-5.136454908305769</v>
+        <v>-2.959728179142953</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.019930756787756</v>
       </c>
       <c r="E78">
-        <v>-11.2675835490547</v>
+        <v>-9.351346187286968</v>
       </c>
       <c r="F78">
-        <v>-3.264409699014729</v>
+        <v>-2.512005243786744</v>
       </c>
       <c r="G78">
-        <v>-4.915098591367941</v>
+        <v>-3.093732441481572</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.990037040147817</v>
       </c>
       <c r="E79">
-        <v>-10.51493305508386</v>
+        <v>-9.958030378568573</v>
       </c>
       <c r="F79">
-        <v>-3.040694999642875</v>
+        <v>-2.796671216656586</v>
       </c>
       <c r="G79">
-        <v>-4.806486213315532</v>
+        <v>-2.6447297710813</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.917505419677481</v>
       </c>
       <c r="E80">
-        <v>-11.83227520086318</v>
+        <v>-10.1704701512164</v>
       </c>
       <c r="F80">
-        <v>-3.275188415659957</v>
+        <v>-2.439023590497899</v>
       </c>
       <c r="G80">
-        <v>-4.810379414869715</v>
+        <v>-3.013249768876351</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.804385655838668</v>
       </c>
       <c r="E81">
-        <v>-12.39770952240892</v>
+        <v>-10.46434094347016</v>
       </c>
       <c r="F81">
-        <v>-3.106806173692901</v>
+        <v>-2.87371518368876</v>
       </c>
       <c r="G81">
-        <v>-4.611385833049662</v>
+        <v>-2.246719433622421</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.656386412886318</v>
       </c>
       <c r="E82">
-        <v>-13.00725570926337</v>
+        <v>-12.03564444007365</v>
       </c>
       <c r="F82">
-        <v>-3.584005440158418</v>
+        <v>-2.778747831162213</v>
       </c>
       <c r="G82">
-        <v>-4.604638941240628</v>
+        <v>-3.146896492296728</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.479363068139591</v>
       </c>
       <c r="E83">
-        <v>-14.57888978446941</v>
+        <v>-12.61488607886877</v>
       </c>
       <c r="F83">
-        <v>-3.862167900548881</v>
+        <v>-2.957234498708617</v>
       </c>
       <c r="G83">
-        <v>-4.388625844803183</v>
+        <v>-2.830222948192204</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.287560832757602</v>
       </c>
       <c r="E84">
-        <v>-15.39278336091999</v>
+        <v>-14.07950325632555</v>
       </c>
       <c r="F84">
-        <v>-3.642897392293046</v>
+        <v>-3.054292650559829</v>
       </c>
       <c r="G84">
-        <v>-4.460914917198709</v>
+        <v>-2.114102289864757</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.087446609589301</v>
       </c>
       <c r="E85">
-        <v>-15.45594198790497</v>
+        <v>-13.28083440948876</v>
       </c>
       <c r="F85">
-        <v>-3.393600222420535</v>
+        <v>-3.002388805835218</v>
       </c>
       <c r="G85">
-        <v>-4.291060757215321</v>
+        <v>-2.529016272847154</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.894998134715485</v>
       </c>
       <c r="E86">
-        <v>-17.66203338548166</v>
+        <v>-16.01494134788581</v>
       </c>
       <c r="F86">
-        <v>-3.838378017107882</v>
+        <v>-3.216922709281845</v>
       </c>
       <c r="G86">
-        <v>-3.759420249063762</v>
+        <v>-2.023525763910297</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.713475447127936</v>
       </c>
       <c r="E87">
-        <v>-18.5387821811587</v>
+        <v>-16.14050687517049</v>
       </c>
       <c r="F87">
-        <v>-4.119827439352653</v>
+        <v>-3.402607889558577</v>
       </c>
       <c r="G87">
-        <v>-4.299909845441793</v>
+        <v>-2.09550695557067</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.554090780942671</v>
       </c>
       <c r="E88">
-        <v>-19.70350569593152</v>
+        <v>-18.03687782146658</v>
       </c>
       <c r="F88">
-        <v>-4.06164125624521</v>
+        <v>-3.221703217563401</v>
       </c>
       <c r="G88">
-        <v>-4.050708529973155</v>
+        <v>-2.433334885671138</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.418992997126736</v>
       </c>
       <c r="E89">
-        <v>-21.29404615011959</v>
+        <v>-19.51688275360141</v>
       </c>
       <c r="F89">
-        <v>-3.940524001547089</v>
+        <v>-3.687390662232213</v>
       </c>
       <c r="G89">
-        <v>-3.578008974602779</v>
+        <v>-1.681854290438736</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.311815983088521</v>
       </c>
       <c r="E90">
-        <v>-21.82869137688717</v>
+        <v>-21.23852705878555</v>
       </c>
       <c r="F90">
-        <v>-4.51602479933542</v>
+        <v>-3.596633072846694</v>
       </c>
       <c r="G90">
-        <v>-4.191277604116149</v>
+        <v>-1.924331887917115</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.233508945213072</v>
       </c>
       <c r="E91">
-        <v>-23.45070019695454</v>
+        <v>-22.88199178870126</v>
       </c>
       <c r="F91">
-        <v>-4.092013347068854</v>
+        <v>-3.817837818988065</v>
       </c>
       <c r="G91">
-        <v>-4.427183768699074</v>
+        <v>-2.476951323151036</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.180402533708459</v>
       </c>
       <c r="E92">
-        <v>-25.19781263995781</v>
+        <v>-24.01869310631461</v>
       </c>
       <c r="F92">
-        <v>-4.421536243167692</v>
+        <v>-3.80512155098769</v>
       </c>
       <c r="G92">
-        <v>-4.786550108078041</v>
+        <v>-2.704134200237982</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.15321918768156</v>
       </c>
       <c r="E93">
-        <v>-27.55333462283961</v>
+        <v>-26.05779702485846</v>
       </c>
       <c r="F93">
-        <v>-4.604293144675527</v>
+        <v>-4.231538582191986</v>
       </c>
       <c r="G93">
-        <v>-5.25391968513019</v>
+        <v>-2.736544441067447</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.1437849135185</v>
       </c>
       <c r="E94">
-        <v>-29.73679270732596</v>
+        <v>-27.57366747113405</v>
       </c>
       <c r="F94">
-        <v>-4.640154826277524</v>
+        <v>-4.115384904971439</v>
       </c>
       <c r="G94">
-        <v>-5.925784970688659</v>
+        <v>-2.824704268778238</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.154363952306604</v>
       </c>
       <c r="E95">
-        <v>-31.58450520040963</v>
+        <v>-30.2408277140387</v>
       </c>
       <c r="F95">
-        <v>-4.589852215742523</v>
+        <v>-4.413370197310894</v>
       </c>
       <c r="G95">
-        <v>-6.045967705400821</v>
+        <v>-3.940421015877875</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.17951178937431</v>
       </c>
       <c r="E96">
-        <v>-33.90512623411431</v>
+        <v>-32.82940761172525</v>
       </c>
       <c r="F96">
-        <v>-4.721331518282263</v>
+        <v>-4.198501633433536</v>
       </c>
       <c r="G96">
-        <v>-6.131942573055694</v>
+        <v>-3.476322257818526</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.219503579411997</v>
       </c>
       <c r="E97">
-        <v>-36.25586388420701</v>
+        <v>-34.36145603139325</v>
       </c>
       <c r="F97">
-        <v>-4.973306799968025</v>
+        <v>-4.245140374945954</v>
       </c>
       <c r="G97">
-        <v>-5.984391558370377</v>
+        <v>-4.051635482724151</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.277521617511716</v>
       </c>
       <c r="E98">
-        <v>-38.22738485666038</v>
+        <v>-37.29373578507696</v>
       </c>
       <c r="F98">
-        <v>-4.762543624938941</v>
+        <v>-4.553894443521802</v>
       </c>
       <c r="G98">
-        <v>-6.145108612665375</v>
+        <v>-4.479791647863633</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.348617533511766</v>
       </c>
       <c r="E99">
-        <v>-41.40508299495279</v>
+        <v>-40.28917190150865</v>
       </c>
       <c r="F99">
-        <v>-4.854759140953388</v>
+        <v>-4.810721473085761</v>
       </c>
       <c r="G99">
-        <v>-7.556427281512075</v>
+        <v>-4.613971369115833</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.450933719700108</v>
       </c>
       <c r="E100">
-        <v>-43.09608538076402</v>
+        <v>-42.48124087932059</v>
       </c>
       <c r="F100">
-        <v>-4.918371958916571</v>
+        <v>-4.792212431837608</v>
       </c>
       <c r="G100">
-        <v>-7.702359439428689</v>
+        <v>-4.860302441601924</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.567173246297609</v>
       </c>
       <c r="E101">
-        <v>-45.20092915647722</v>
+        <v>-44.20456298412456</v>
       </c>
       <c r="F101">
-        <v>-5.195472452296644</v>
+        <v>-5.024123826660164</v>
       </c>
       <c r="G101">
-        <v>-7.780276439240975</v>
+        <v>-6.104196890891062</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.7438723438642</v>
       </c>
       <c r="E102">
-        <v>-47.95459683835039</v>
+        <v>-47.1657276092662</v>
       </c>
       <c r="F102">
-        <v>-5.057066341534695</v>
+        <v>-5.084857239531216</v>
       </c>
       <c r="G102">
-        <v>-8.201023603463568</v>
+        <v>-5.835850690568818</v>
       </c>
     </row>
   </sheetData>
